--- a/artfynd/A 41922-2025 artfynd.xlsx
+++ b/artfynd/A 41922-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121084585</v>
+        <v>121084587</v>
       </c>
       <c r="B2" t="n">
-        <v>78340</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545842</v>
+        <v>545897</v>
       </c>
       <c r="R2" t="n">
-        <v>6881347</v>
+        <v>6881150</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,16 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>yngre produktionsskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>relikt brandstubbe</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121084584</v>
+        <v>121084580</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545794</v>
+        <v>546151</v>
       </c>
       <c r="R3" t="n">
-        <v>6881363</v>
+        <v>6881221</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,53 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121084583</v>
+        <v>121084584</v>
       </c>
       <c r="B4" t="n">
-        <v>77988</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor myran N, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545765</v>
+        <v>545794</v>
       </c>
       <c r="R4" t="n">
-        <v>6881350</v>
+        <v>6881363</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121084581</v>
+        <v>121084583</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,34 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor myran N, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545967</v>
+        <v>545765</v>
       </c>
       <c r="R5" t="n">
-        <v>6881248</v>
+        <v>6881350</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,13 +1048,9 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1099,6 +1064,215 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121084581</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor myran N, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545967</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6881248</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121084585</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor myran N, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>545842</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6881347</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>yngre produktionsskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>relikt brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41922-2025 artfynd.xlsx
+++ b/artfynd/A 41922-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121084587</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121084580</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121084584</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121084583</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121084581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,8 +1303,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121084585</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>